--- a/data/uploads_local/사모_판매대본_라이프META일반사모투자신탁 제2호.xlsx
+++ b/data/uploads_local/사모_판매대본_라이프META일반사모투자신탁 제2호.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a114384/Desktop/2.KISAI/펀드 불완전판매/data/uploads_local/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D304EF9-FED5-BC43-9893-3A8612B9C744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DED12C-2761-B748-A72E-F800532E5D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6020" yWindow="760" windowWidth="28540" windowHeight="20440" activeTab="1" xr2:uid="{27046729-DC8E-4EC9-9EBE-9FEAE0333B25}"/>
+    <workbookView xWindow="3740" yWindow="1900" windowWidth="28540" windowHeight="20440" xr2:uid="{27046729-DC8E-4EC9-9EBE-9FEAE0333B25}"/>
   </bookViews>
   <sheets>
     <sheet name="사모펀드(내점)" sheetId="78" r:id="rId1"/>
@@ -4603,241 +4603,262 @@
     <xf numFmtId="0" fontId="28" fillId="7" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4846,15 +4867,27 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4871,39 +4904,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5093,8 +5093,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12657745" y="36424022"/>
-          <a:ext cx="6134956" cy="1617148"/>
+          <a:off x="12698756" y="37406684"/>
+          <a:ext cx="6134956" cy="1608417"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5527,32 +5527,32 @@
       <c r="A5" s="179" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="199"/>
-      <c r="C5" s="173" t="s">
+      <c r="B5" s="180"/>
+      <c r="C5" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="172" t="s">
+      <c r="D5" s="104" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="172"/>
-      <c r="F5" s="172" t="s">
+      <c r="E5" s="104"/>
+      <c r="F5" s="104" t="s">
         <v>165</v>
       </c>
-      <c r="G5" s="172"/>
-      <c r="H5" s="104" t="s">
+      <c r="G5" s="104"/>
+      <c r="H5" s="176" t="s">
         <v>166</v>
       </c>
-      <c r="I5" s="173" t="s">
+      <c r="I5" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="173" t="s">
+      <c r="J5" s="105" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="180"/>
-      <c r="B6" s="200"/>
-      <c r="C6" s="174"/>
+      <c r="A6" s="181"/>
+      <c r="B6" s="182"/>
+      <c r="C6" s="106"/>
       <c r="D6" s="73" t="s">
         <v>167</v>
       </c>
@@ -5565,15 +5565,15 @@
       <c r="G6" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="H6" s="104"/>
-      <c r="I6" s="174"/>
-      <c r="J6" s="174"/>
+      <c r="H6" s="176"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="106"/>
     </row>
     <row r="7" spans="1:10" ht="51.75" customHeight="1">
-      <c r="A7" s="201" t="s">
+      <c r="A7" s="183" t="s">
         <v>152</v>
       </c>
-      <c r="B7" s="202"/>
+      <c r="B7" s="184"/>
       <c r="C7" s="19"/>
       <c r="D7" s="70" t="s">
         <v>3</v>
@@ -5596,29 +5596,29 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="59.25" customHeight="1">
-      <c r="A8" s="186" t="s">
+      <c r="A8" s="197" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="187"/>
-      <c r="C8" s="115" t="s">
+      <c r="B8" s="198"/>
+      <c r="C8" s="113" t="s">
         <v>158</v>
       </c>
-      <c r="D8" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="126" t="s">
+      <c r="D8" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="139" t="s">
         <v>163</v>
       </c>
       <c r="J8" s="45" t="s">
@@ -5626,57 +5626,57 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A9" s="188"/>
-      <c r="B9" s="189"/>
-      <c r="C9" s="116"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="130"/>
+      <c r="A9" s="199"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="114"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="130"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="175"/>
       <c r="J9" s="44" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="60" customHeight="1">
-      <c r="A10" s="190"/>
-      <c r="B10" s="191"/>
-      <c r="C10" s="131"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
-      <c r="I10" s="127"/>
+      <c r="A10" s="201"/>
+      <c r="B10" s="202"/>
+      <c r="C10" s="115"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="131"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="140"/>
       <c r="J10" s="72" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="60" customHeight="1">
-      <c r="A11" s="183" t="s">
+      <c r="A11" s="185" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="183"/>
-      <c r="C11" s="143" t="s">
+      <c r="B11" s="185"/>
+      <c r="C11" s="128" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="G11" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="H11" s="184" t="s">
-        <v>3</v>
-      </c>
-      <c r="I11" s="185" t="s">
+      <c r="D11" s="196" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="196" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="196" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="196" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="196" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="186" t="s">
         <v>105</v>
       </c>
       <c r="J11" s="75" t="s">
@@ -5684,24 +5684,24 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1">
-      <c r="A12" s="183"/>
-      <c r="B12" s="183"/>
-      <c r="C12" s="143"/>
-      <c r="D12" s="184"/>
-      <c r="E12" s="184"/>
-      <c r="F12" s="184"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="185"/>
+      <c r="A12" s="185"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="128"/>
+      <c r="D12" s="196"/>
+      <c r="E12" s="196"/>
+      <c r="F12" s="196"/>
+      <c r="G12" s="196"/>
+      <c r="H12" s="196"/>
+      <c r="I12" s="186"/>
       <c r="J12" s="74" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="127.5" customHeight="1">
-      <c r="A13" s="166" t="s">
+      <c r="A13" s="135" t="s">
         <v>171</v>
       </c>
-      <c r="B13" s="167"/>
+      <c r="B13" s="136"/>
       <c r="C13" s="71" t="s">
         <v>172</v>
       </c>
@@ -5728,10 +5728,10 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="58.5" customHeight="1">
-      <c r="A14" s="161" t="s">
+      <c r="A14" s="126" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="161"/>
+      <c r="B14" s="126"/>
       <c r="C14" s="47" t="s">
         <v>94</v>
       </c>
@@ -5756,56 +5756,56 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="95.25" customHeight="1">
-      <c r="A15" s="162" t="s">
+      <c r="A15" s="127" t="s">
         <v>185</v>
       </c>
-      <c r="B15" s="162"/>
-      <c r="C15" s="115" t="s">
+      <c r="B15" s="127"/>
+      <c r="C15" s="113" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="112"/>
-      <c r="F15" s="168"/>
+      <c r="D15" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="163"/>
+      <c r="F15" s="137"/>
       <c r="G15" s="79"/>
       <c r="H15" s="79"/>
-      <c r="I15" s="163"/>
+      <c r="I15" s="132"/>
       <c r="J15" s="12" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="33.75" customHeight="1">
-      <c r="A16" s="162"/>
-      <c r="B16" s="162"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="108"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="169"/>
+      <c r="A16" s="127"/>
+      <c r="B16" s="127"/>
+      <c r="C16" s="114"/>
+      <c r="D16" s="130"/>
+      <c r="E16" s="164"/>
+      <c r="F16" s="138"/>
       <c r="G16" s="79"/>
       <c r="H16" s="79"/>
-      <c r="I16" s="163"/>
+      <c r="I16" s="132"/>
       <c r="J16" s="49" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="60" customHeight="1">
-      <c r="A17" s="162"/>
-      <c r="B17" s="162"/>
-      <c r="C17" s="131"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="117"/>
-      <c r="F17" s="169"/>
+      <c r="A17" s="127"/>
+      <c r="B17" s="127"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="165"/>
+      <c r="F17" s="138"/>
       <c r="G17" s="79"/>
       <c r="H17" s="79"/>
-      <c r="I17" s="163"/>
+      <c r="I17" s="132"/>
       <c r="J17" s="12" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="105.75" customHeight="1">
-      <c r="A18" s="162"/>
-      <c r="B18" s="162"/>
+      <c r="A18" s="127"/>
+      <c r="B18" s="127"/>
       <c r="C18" s="153" t="s">
         <v>97</v>
       </c>
@@ -5816,7 +5816,7 @@
       <c r="F18" s="79"/>
       <c r="G18" s="79"/>
       <c r="H18" s="79"/>
-      <c r="I18" s="181" t="s">
+      <c r="I18" s="188" t="s">
         <v>98</v>
       </c>
       <c r="J18" s="13" t="s">
@@ -5824,8 +5824,8 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="93.75" customHeight="1">
-      <c r="A19" s="162"/>
-      <c r="B19" s="162"/>
+      <c r="A19" s="127"/>
+      <c r="B19" s="127"/>
       <c r="C19" s="154"/>
       <c r="D19" s="18" t="s">
         <v>3</v>
@@ -5834,7 +5834,7 @@
       <c r="F19" s="79"/>
       <c r="G19" s="79"/>
       <c r="H19" s="79"/>
-      <c r="I19" s="182"/>
+      <c r="I19" s="189"/>
       <c r="J19" s="12" t="s">
         <v>99</v>
       </c>
@@ -5847,15 +5847,15 @@
       <c r="C20" s="153" t="s">
         <v>101</v>
       </c>
-      <c r="D20" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="112"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="126"/>
-      <c r="J20" s="126" t="s">
+      <c r="D20" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="163"/>
+      <c r="F20" s="178"/>
+      <c r="G20" s="170"/>
+      <c r="H20" s="170"/>
+      <c r="I20" s="139"/>
+      <c r="J20" s="139" t="s">
         <v>176</v>
       </c>
     </row>
@@ -5863,13 +5863,13 @@
       <c r="A21" s="151"/>
       <c r="B21" s="152"/>
       <c r="C21" s="154"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="127"/>
-      <c r="J21" s="127"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="165"/>
+      <c r="F21" s="178"/>
+      <c r="G21" s="171"/>
+      <c r="H21" s="171"/>
+      <c r="I21" s="140"/>
+      <c r="J21" s="140"/>
     </row>
     <row r="22" spans="1:10" ht="115.5" customHeight="1">
       <c r="A22" s="146" t="s">
@@ -5890,23 +5890,23 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="58.5" customHeight="1">
-      <c r="A23" s="194" t="s">
+      <c r="A23" s="193" t="s">
         <v>187</v>
       </c>
       <c r="B23" s="150" t="s">
         <v>177</v>
       </c>
-      <c r="C23" s="115" t="s">
+      <c r="C23" s="113" t="s">
         <v>179</v>
       </c>
-      <c r="D23" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="E23" s="112"/>
-      <c r="F23" s="112"/>
-      <c r="G23" s="112"/>
-      <c r="H23" s="112"/>
-      <c r="I23" s="126" t="s">
+      <c r="D23" s="129" t="s">
+        <v>0</v>
+      </c>
+      <c r="E23" s="163"/>
+      <c r="F23" s="163"/>
+      <c r="G23" s="163"/>
+      <c r="H23" s="163"/>
+      <c r="I23" s="139" t="s">
         <v>180</v>
       </c>
       <c r="J23" s="52" t="s">
@@ -5914,36 +5914,36 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="33.75" customHeight="1">
-      <c r="A24" s="195"/>
+      <c r="A24" s="194"/>
       <c r="B24" s="148"/>
-      <c r="C24" s="116"/>
-      <c r="D24" s="108"/>
-      <c r="E24" s="113"/>
-      <c r="F24" s="113"/>
-      <c r="G24" s="113"/>
-      <c r="H24" s="113"/>
-      <c r="I24" s="130"/>
+      <c r="C24" s="114"/>
+      <c r="D24" s="130"/>
+      <c r="E24" s="164"/>
+      <c r="F24" s="164"/>
+      <c r="G24" s="164"/>
+      <c r="H24" s="164"/>
+      <c r="I24" s="175"/>
       <c r="J24" s="17" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A25" s="195"/>
-      <c r="B25" s="196"/>
-      <c r="C25" s="116"/>
-      <c r="D25" s="129"/>
-      <c r="E25" s="114"/>
-      <c r="F25" s="114"/>
-      <c r="G25" s="114"/>
-      <c r="H25" s="114"/>
-      <c r="I25" s="197"/>
+      <c r="A25" s="194"/>
+      <c r="B25" s="195"/>
+      <c r="C25" s="114"/>
+      <c r="D25" s="173"/>
+      <c r="E25" s="174"/>
+      <c r="F25" s="174"/>
+      <c r="G25" s="174"/>
+      <c r="H25" s="174"/>
+      <c r="I25" s="190"/>
       <c r="J25" s="84" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="144.75" customHeight="1">
-      <c r="A26" s="195"/>
-      <c r="B26" s="192" t="s">
+      <c r="A26" s="194"/>
+      <c r="B26" s="191" t="s">
         <v>178</v>
       </c>
       <c r="C26" s="59" t="s">
@@ -5966,8 +5966,8 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A27" s="195"/>
-      <c r="B27" s="193"/>
+      <c r="A27" s="194"/>
+      <c r="B27" s="192"/>
       <c r="C27" s="80" t="s">
         <v>179</v>
       </c>
@@ -5986,10 +5986,10 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="58.5" customHeight="1" thickTop="1">
-      <c r="A28" s="120" t="s">
+      <c r="A28" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="120"/>
+      <c r="B28" s="143"/>
       <c r="C28" s="24"/>
       <c r="D28" s="18" t="s">
         <v>0</v>
@@ -6014,28 +6014,28 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="124.5" customHeight="1">
-      <c r="A29" s="183" t="s">
+      <c r="A29" s="185" t="s">
         <v>188</v>
       </c>
-      <c r="B29" s="183" t="s">
+      <c r="B29" s="185" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="143" t="s">
+      <c r="C29" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="D29" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="102" t="s">
+      <c r="D29" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="129" t="s">
         <v>3</v>
       </c>
       <c r="I29" s="144" t="s">
@@ -6046,35 +6046,35 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="141" customHeight="1">
-      <c r="A30" s="183"/>
-      <c r="B30" s="183"/>
-      <c r="C30" s="143"/>
-      <c r="D30" s="108"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="108"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="108"/>
+      <c r="A30" s="185"/>
+      <c r="B30" s="185"/>
+      <c r="C30" s="128"/>
+      <c r="D30" s="130"/>
+      <c r="E30" s="130"/>
+      <c r="F30" s="130"/>
+      <c r="G30" s="130"/>
+      <c r="H30" s="130"/>
       <c r="I30" s="144"/>
       <c r="J30" s="145"/>
     </row>
     <row r="31" spans="1:10" ht="165" customHeight="1">
-      <c r="A31" s="183"/>
+      <c r="A31" s="185"/>
       <c r="B31" s="90" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="14"/>
-      <c r="D31" s="103"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="103"/>
-      <c r="G31" s="103"/>
-      <c r="H31" s="103"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="131"/>
+      <c r="G31" s="131"/>
+      <c r="H31" s="131"/>
       <c r="I31" s="144"/>
       <c r="J31" s="25" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="48">
-      <c r="A32" s="183"/>
+      <c r="A32" s="185"/>
       <c r="B32" s="90" t="s">
         <v>147</v>
       </c>
@@ -6100,7 +6100,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="50.25" customHeight="1">
-      <c r="A33" s="183"/>
+      <c r="A33" s="185"/>
       <c r="B33" s="90" t="s">
         <v>8</v>
       </c>
@@ -6154,17 +6154,17 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="169.5" customHeight="1">
-      <c r="A35" s="135" t="s">
+      <c r="A35" s="155" t="s">
         <v>189</v>
       </c>
       <c r="B35" s="65" t="s">
         <v>57</v>
       </c>
       <c r="C35" s="26"/>
-      <c r="D35" s="115" t="s">
-        <v>0</v>
-      </c>
-      <c r="E35" s="115" t="s">
+      <c r="D35" s="113" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="113" t="s">
         <v>0</v>
       </c>
       <c r="F35" s="18" t="s">
@@ -6184,11 +6184,11 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="320.25" customHeight="1">
-      <c r="A36" s="136"/>
+      <c r="A36" s="156"/>
       <c r="B36" s="91"/>
       <c r="C36" s="26"/>
-      <c r="D36" s="116"/>
-      <c r="E36" s="116"/>
+      <c r="D36" s="114"/>
+      <c r="E36" s="114"/>
       <c r="F36" s="18"/>
       <c r="G36" s="18"/>
       <c r="H36" s="18"/>
@@ -6198,11 +6198,11 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="121.5" customHeight="1">
-      <c r="A37" s="136"/>
+      <c r="A37" s="156"/>
       <c r="B37" s="66"/>
       <c r="C37" s="26"/>
-      <c r="D37" s="116"/>
-      <c r="E37" s="116"/>
+      <c r="D37" s="114"/>
+      <c r="E37" s="114"/>
       <c r="F37" s="18"/>
       <c r="G37" s="18"/>
       <c r="H37" s="18"/>
@@ -6212,13 +6212,13 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="237.75" customHeight="1">
-      <c r="A38" s="136"/>
+      <c r="A38" s="156"/>
       <c r="B38" s="91" t="s">
         <v>90</v>
       </c>
       <c r="C38" s="26"/>
-      <c r="D38" s="116"/>
-      <c r="E38" s="116"/>
+      <c r="D38" s="114"/>
+      <c r="E38" s="114"/>
       <c r="F38" s="38"/>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
@@ -6230,177 +6230,177 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A39" s="136"/>
+      <c r="A39" s="156"/>
       <c r="B39" s="89" t="s">
         <v>58</v>
       </c>
       <c r="C39" s="14"/>
-      <c r="D39" s="115" t="s">
-        <v>3</v>
-      </c>
-      <c r="E39" s="115" t="s">
-        <v>3</v>
-      </c>
-      <c r="F39" s="115" t="s">
-        <v>3</v>
-      </c>
-      <c r="G39" s="115" t="s">
-        <v>3</v>
-      </c>
-      <c r="H39" s="115" t="s">
-        <v>3</v>
-      </c>
-      <c r="I39" s="115"/>
+      <c r="D39" s="113" t="s">
+        <v>3</v>
+      </c>
+      <c r="E39" s="113" t="s">
+        <v>3</v>
+      </c>
+      <c r="F39" s="113" t="s">
+        <v>3</v>
+      </c>
+      <c r="G39" s="113" t="s">
+        <v>3</v>
+      </c>
+      <c r="H39" s="113" t="s">
+        <v>3</v>
+      </c>
+      <c r="I39" s="113"/>
       <c r="J39" s="9" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A40" s="136"/>
+      <c r="A40" s="156"/>
       <c r="B40" s="89" t="s">
         <v>59</v>
       </c>
       <c r="C40" s="14"/>
-      <c r="D40" s="116"/>
-      <c r="E40" s="116"/>
-      <c r="F40" s="116"/>
-      <c r="G40" s="116"/>
-      <c r="H40" s="116"/>
-      <c r="I40" s="116"/>
+      <c r="D40" s="114"/>
+      <c r="E40" s="114"/>
+      <c r="F40" s="114"/>
+      <c r="G40" s="114"/>
+      <c r="H40" s="114"/>
+      <c r="I40" s="114"/>
       <c r="J40" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="16">
-      <c r="A41" s="136"/>
+      <c r="A41" s="156"/>
       <c r="B41" s="89" t="s">
         <v>60</v>
       </c>
       <c r="C41" s="14"/>
-      <c r="D41" s="116"/>
-      <c r="E41" s="116"/>
-      <c r="F41" s="116"/>
-      <c r="G41" s="116"/>
-      <c r="H41" s="116"/>
-      <c r="I41" s="116"/>
+      <c r="D41" s="114"/>
+      <c r="E41" s="114"/>
+      <c r="F41" s="114"/>
+      <c r="G41" s="114"/>
+      <c r="H41" s="114"/>
+      <c r="I41" s="114"/>
       <c r="J41" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="16">
-      <c r="A42" s="136"/>
+      <c r="A42" s="156"/>
       <c r="B42" s="89" t="s">
         <v>61</v>
       </c>
       <c r="C42" s="14"/>
-      <c r="D42" s="116"/>
-      <c r="E42" s="116"/>
-      <c r="F42" s="116"/>
-      <c r="G42" s="116"/>
-      <c r="H42" s="116"/>
-      <c r="I42" s="116"/>
+      <c r="D42" s="114"/>
+      <c r="E42" s="114"/>
+      <c r="F42" s="114"/>
+      <c r="G42" s="114"/>
+      <c r="H42" s="114"/>
+      <c r="I42" s="114"/>
       <c r="J42" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="16">
-      <c r="A43" s="136"/>
+      <c r="A43" s="156"/>
       <c r="B43" s="89" t="s">
         <v>62</v>
       </c>
       <c r="C43" s="14"/>
-      <c r="D43" s="116"/>
-      <c r="E43" s="116"/>
-      <c r="F43" s="116"/>
-      <c r="G43" s="116"/>
-      <c r="H43" s="116"/>
-      <c r="I43" s="116"/>
+      <c r="D43" s="114"/>
+      <c r="E43" s="114"/>
+      <c r="F43" s="114"/>
+      <c r="G43" s="114"/>
+      <c r="H43" s="114"/>
+      <c r="I43" s="114"/>
       <c r="J43" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A44" s="136"/>
+      <c r="A44" s="156"/>
       <c r="B44" s="89" t="s">
         <v>63</v>
       </c>
       <c r="C44" s="14"/>
-      <c r="D44" s="116"/>
-      <c r="E44" s="116"/>
-      <c r="F44" s="116"/>
-      <c r="G44" s="116"/>
-      <c r="H44" s="116"/>
-      <c r="I44" s="116"/>
+      <c r="D44" s="114"/>
+      <c r="E44" s="114"/>
+      <c r="F44" s="114"/>
+      <c r="G44" s="114"/>
+      <c r="H44" s="114"/>
+      <c r="I44" s="114"/>
       <c r="J44" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16">
-      <c r="A45" s="136"/>
+      <c r="A45" s="156"/>
       <c r="B45" s="89" t="s">
         <v>64</v>
       </c>
       <c r="C45" s="14"/>
-      <c r="D45" s="116"/>
-      <c r="E45" s="116"/>
-      <c r="F45" s="116"/>
-      <c r="G45" s="116"/>
-      <c r="H45" s="116"/>
-      <c r="I45" s="116"/>
+      <c r="D45" s="114"/>
+      <c r="E45" s="114"/>
+      <c r="F45" s="114"/>
+      <c r="G45" s="114"/>
+      <c r="H45" s="114"/>
+      <c r="I45" s="114"/>
       <c r="J45" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A46" s="136"/>
+      <c r="A46" s="156"/>
       <c r="B46" s="89" t="s">
         <v>5</v>
       </c>
       <c r="C46" s="14"/>
-      <c r="D46" s="116"/>
-      <c r="E46" s="116"/>
-      <c r="F46" s="116"/>
-      <c r="G46" s="116"/>
-      <c r="H46" s="116"/>
-      <c r="I46" s="116"/>
+      <c r="D46" s="114"/>
+      <c r="E46" s="114"/>
+      <c r="F46" s="114"/>
+      <c r="G46" s="114"/>
+      <c r="H46" s="114"/>
+      <c r="I46" s="114"/>
       <c r="J46" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16">
-      <c r="A47" s="136"/>
+      <c r="A47" s="156"/>
       <c r="B47" s="89" t="s">
         <v>72</v>
       </c>
       <c r="C47" s="14"/>
-      <c r="D47" s="116"/>
-      <c r="E47" s="116"/>
-      <c r="F47" s="116"/>
-      <c r="G47" s="116"/>
-      <c r="H47" s="116"/>
-      <c r="I47" s="116"/>
+      <c r="D47" s="114"/>
+      <c r="E47" s="114"/>
+      <c r="F47" s="114"/>
+      <c r="G47" s="114"/>
+      <c r="H47" s="114"/>
+      <c r="I47" s="114"/>
       <c r="J47" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="18" customHeight="1">
-      <c r="A48" s="136"/>
+      <c r="A48" s="156"/>
       <c r="B48" s="89" t="s">
         <v>70</v>
       </c>
       <c r="C48" s="14"/>
-      <c r="D48" s="131"/>
-      <c r="E48" s="131"/>
-      <c r="F48" s="131"/>
-      <c r="G48" s="131"/>
-      <c r="H48" s="131"/>
-      <c r="I48" s="116"/>
+      <c r="D48" s="115"/>
+      <c r="E48" s="115"/>
+      <c r="F48" s="115"/>
+      <c r="G48" s="115"/>
+      <c r="H48" s="115"/>
+      <c r="I48" s="114"/>
       <c r="J48" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="33" customHeight="1">
-      <c r="A49" s="136"/>
+      <c r="A49" s="156"/>
       <c r="B49" s="89" t="s">
         <v>78</v>
       </c>
@@ -6420,13 +6420,13 @@
       <c r="H49" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="I49" s="116"/>
+      <c r="I49" s="114"/>
       <c r="J49" s="35" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A50" s="136"/>
+      <c r="A50" s="156"/>
       <c r="B50" s="89" t="s">
         <v>79</v>
       </c>
@@ -6446,13 +6446,13 @@
       <c r="H50" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="I50" s="131"/>
+      <c r="I50" s="115"/>
       <c r="J50" s="35" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="32">
-      <c r="A51" s="136"/>
+      <c r="A51" s="156"/>
       <c r="B51" s="89" t="s">
         <v>127</v>
       </c>
@@ -6480,7 +6480,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="44.25" customHeight="1">
-      <c r="A52" s="136"/>
+      <c r="A52" s="156"/>
       <c r="B52" s="89" t="s">
         <v>65</v>
       </c>
@@ -6506,7 +6506,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="44.25" customHeight="1">
-      <c r="A53" s="136"/>
+      <c r="A53" s="156"/>
       <c r="B53" s="89" t="s">
         <v>71</v>
       </c>
@@ -6532,7 +6532,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="32">
-      <c r="A54" s="136"/>
+      <c r="A54" s="156"/>
       <c r="B54" s="89" t="s">
         <v>46</v>
       </c>
@@ -6558,7 +6558,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="32">
-      <c r="A55" s="136"/>
+      <c r="A55" s="156"/>
       <c r="B55" s="89" t="s">
         <v>66</v>
       </c>
@@ -6584,7 +6584,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="32">
-      <c r="A56" s="198"/>
+      <c r="A56" s="187"/>
       <c r="B56" s="89" t="s">
         <v>148</v>
       </c>
@@ -6612,27 +6612,27 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="27" customHeight="1">
-      <c r="A57" s="137" t="s">
+      <c r="A57" s="157" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="138"/>
-      <c r="C57" s="143"/>
-      <c r="D57" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="185" t="s">
+      <c r="B57" s="158"/>
+      <c r="C57" s="128"/>
+      <c r="D57" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="186" t="s">
         <v>19</v>
       </c>
       <c r="J57" s="30" t="s">
@@ -6640,91 +6640,91 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="27" customHeight="1">
-      <c r="A58" s="139"/>
-      <c r="B58" s="140"/>
-      <c r="C58" s="143"/>
-      <c r="D58" s="108"/>
-      <c r="E58" s="108"/>
-      <c r="F58" s="108"/>
-      <c r="G58" s="109"/>
-      <c r="H58" s="109"/>
-      <c r="I58" s="185"/>
+      <c r="A58" s="159"/>
+      <c r="B58" s="160"/>
+      <c r="C58" s="128"/>
+      <c r="D58" s="130"/>
+      <c r="E58" s="130"/>
+      <c r="F58" s="130"/>
+      <c r="G58" s="177"/>
+      <c r="H58" s="177"/>
+      <c r="I58" s="186"/>
       <c r="J58" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="27" customHeight="1">
-      <c r="A59" s="139"/>
-      <c r="B59" s="140"/>
-      <c r="C59" s="143"/>
-      <c r="D59" s="108"/>
-      <c r="E59" s="108"/>
-      <c r="F59" s="108"/>
-      <c r="G59" s="109"/>
-      <c r="H59" s="109"/>
-      <c r="I59" s="185"/>
+      <c r="A59" s="159"/>
+      <c r="B59" s="160"/>
+      <c r="C59" s="128"/>
+      <c r="D59" s="130"/>
+      <c r="E59" s="130"/>
+      <c r="F59" s="130"/>
+      <c r="G59" s="177"/>
+      <c r="H59" s="177"/>
+      <c r="I59" s="186"/>
       <c r="J59" s="30" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="27" customHeight="1">
-      <c r="A60" s="139"/>
-      <c r="B60" s="140"/>
-      <c r="C60" s="143"/>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="185"/>
+      <c r="A60" s="159"/>
+      <c r="B60" s="160"/>
+      <c r="C60" s="128"/>
+      <c r="D60" s="130"/>
+      <c r="E60" s="130"/>
+      <c r="F60" s="130"/>
+      <c r="G60" s="177"/>
+      <c r="H60" s="177"/>
+      <c r="I60" s="186"/>
       <c r="J60" s="15" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="27" customHeight="1">
-      <c r="A61" s="139"/>
-      <c r="B61" s="140"/>
-      <c r="C61" s="143"/>
-      <c r="D61" s="108"/>
-      <c r="E61" s="108"/>
-      <c r="F61" s="108"/>
-      <c r="G61" s="109"/>
-      <c r="H61" s="109"/>
-      <c r="I61" s="185"/>
+      <c r="A61" s="159"/>
+      <c r="B61" s="160"/>
+      <c r="C61" s="128"/>
+      <c r="D61" s="130"/>
+      <c r="E61" s="130"/>
+      <c r="F61" s="130"/>
+      <c r="G61" s="177"/>
+      <c r="H61" s="177"/>
+      <c r="I61" s="186"/>
       <c r="J61" s="30" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="27" customHeight="1">
-      <c r="A62" s="139"/>
-      <c r="B62" s="140"/>
-      <c r="C62" s="143"/>
-      <c r="D62" s="108"/>
-      <c r="E62" s="108"/>
-      <c r="F62" s="108"/>
-      <c r="G62" s="109"/>
-      <c r="H62" s="109"/>
-      <c r="I62" s="185"/>
+      <c r="A62" s="159"/>
+      <c r="B62" s="160"/>
+      <c r="C62" s="128"/>
+      <c r="D62" s="130"/>
+      <c r="E62" s="130"/>
+      <c r="F62" s="130"/>
+      <c r="G62" s="177"/>
+      <c r="H62" s="177"/>
+      <c r="I62" s="186"/>
       <c r="J62" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="32">
-      <c r="A63" s="141"/>
-      <c r="B63" s="142"/>
-      <c r="C63" s="143"/>
-      <c r="D63" s="103"/>
-      <c r="E63" s="103"/>
-      <c r="F63" s="103"/>
-      <c r="G63" s="109"/>
-      <c r="H63" s="109"/>
-      <c r="I63" s="185"/>
+      <c r="A63" s="161"/>
+      <c r="B63" s="162"/>
+      <c r="C63" s="128"/>
+      <c r="D63" s="131"/>
+      <c r="E63" s="131"/>
+      <c r="F63" s="131"/>
+      <c r="G63" s="177"/>
+      <c r="H63" s="177"/>
+      <c r="I63" s="186"/>
       <c r="J63" s="30" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="54" hidden="1" customHeight="1">
-      <c r="A64" s="120" t="s">
+      <c r="A64" s="143" t="s">
         <v>51</v>
       </c>
       <c r="B64" s="89"/>
@@ -6750,7 +6750,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="48">
-      <c r="A65" s="120"/>
+      <c r="A65" s="143"/>
       <c r="B65" s="89" t="s">
         <v>52</v>
       </c>
@@ -6883,58 +6883,21 @@
     </row>
   </sheetData>
   <mergeCells count="83">
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:A33"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="I29:I33"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="G29:G31"/>
-    <mergeCell ref="H29:H31"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="I39:I50"/>
-    <mergeCell ref="G57:G63"/>
-    <mergeCell ref="H57:H63"/>
-    <mergeCell ref="I57:I63"/>
-    <mergeCell ref="A57:B63"/>
-    <mergeCell ref="C57:C63"/>
-    <mergeCell ref="F57:F63"/>
-    <mergeCell ref="F39:F48"/>
-    <mergeCell ref="G39:G48"/>
-    <mergeCell ref="H39:H48"/>
-    <mergeCell ref="A35:A56"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="A20:B21"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="H23:H25"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I23:I25"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A23:A27"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="E57:E63"/>
+    <mergeCell ref="D57:D63"/>
+    <mergeCell ref="D39:D48"/>
+    <mergeCell ref="E39:E48"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="D35:D38"/>
+    <mergeCell ref="E35:E38"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
     <mergeCell ref="A11:B12"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="D5:E5"/>
@@ -6951,21 +6914,58 @@
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="A8:B10"/>
     <mergeCell ref="I8:I10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="E57:E63"/>
-    <mergeCell ref="D57:D63"/>
-    <mergeCell ref="D39:D48"/>
-    <mergeCell ref="E39:E48"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="D35:D38"/>
-    <mergeCell ref="E35:E38"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="H23:H25"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I23:I25"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="I39:I50"/>
+    <mergeCell ref="G57:G63"/>
+    <mergeCell ref="H57:H63"/>
+    <mergeCell ref="I57:I63"/>
+    <mergeCell ref="A57:B63"/>
+    <mergeCell ref="C57:C63"/>
+    <mergeCell ref="F57:F63"/>
+    <mergeCell ref="F39:F48"/>
+    <mergeCell ref="G39:G48"/>
+    <mergeCell ref="H39:H48"/>
+    <mergeCell ref="A35:A56"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="H29:H31"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="I29:I33"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7015,18 +7015,18 @@
       <c r="J1" s="5"/>
     </row>
     <row r="2" spans="1:10" ht="244.5" customHeight="1">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="166" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="62" t="s">
@@ -7048,35 +7048,35 @@
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="50.25" customHeight="1">
-      <c r="A5" s="172" t="s">
+      <c r="A5" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="172"/>
-      <c r="C5" s="172" t="s">
+      <c r="B5" s="104"/>
+      <c r="C5" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="172" t="s">
+      <c r="D5" s="104" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="172"/>
-      <c r="F5" s="172" t="s">
+      <c r="E5" s="104"/>
+      <c r="F5" s="104" t="s">
         <v>165</v>
       </c>
-      <c r="G5" s="172"/>
-      <c r="H5" s="104" t="s">
+      <c r="G5" s="104"/>
+      <c r="H5" s="176" t="s">
         <v>166</v>
       </c>
-      <c r="I5" s="173" t="s">
+      <c r="I5" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="172" t="s">
+      <c r="J5" s="104" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="172"/>
-      <c r="B6" s="172"/>
-      <c r="C6" s="172"/>
+      <c r="A6" s="104"/>
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
       <c r="D6" s="73" t="s">
         <v>167</v>
       </c>
@@ -7089,34 +7089,34 @@
       <c r="G6" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="H6" s="104"/>
-      <c r="I6" s="174"/>
-      <c r="J6" s="172"/>
+      <c r="H6" s="176"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="104"/>
     </row>
     <row r="7" spans="1:10" ht="204" customHeight="1">
-      <c r="A7" s="157" t="s">
+      <c r="A7" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="158"/>
-      <c r="C7" s="115" t="s">
+      <c r="B7" s="108"/>
+      <c r="C7" s="113" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="105" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="105" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="105" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="105" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="105" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="132" t="s">
+      <c r="D7" s="119" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="119" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="119" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="119" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="119" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="116" t="s">
         <v>134</v>
       </c>
       <c r="J7" s="42" t="s">
@@ -7124,66 +7124,66 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="86.25" customHeight="1">
-      <c r="A8" s="175"/>
-      <c r="B8" s="176"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="106"/>
-      <c r="E8" s="106"/>
-      <c r="F8" s="106"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="106"/>
-      <c r="I8" s="133"/>
+      <c r="A8" s="109"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="114"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="120"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="117"/>
       <c r="J8" s="36" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="48">
-      <c r="A9" s="175"/>
-      <c r="B9" s="176"/>
-      <c r="C9" s="116"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="106"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="133"/>
+      <c r="A9" s="109"/>
+      <c r="B9" s="110"/>
+      <c r="C9" s="114"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="120"/>
+      <c r="I9" s="117"/>
       <c r="J9" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="128">
-      <c r="A10" s="175"/>
-      <c r="B10" s="176"/>
-      <c r="C10" s="116"/>
-      <c r="D10" s="106"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="133"/>
+      <c r="A10" s="109"/>
+      <c r="B10" s="110"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="120"/>
+      <c r="I10" s="117"/>
       <c r="J10" s="16" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="48">
-      <c r="A11" s="159"/>
-      <c r="B11" s="160"/>
-      <c r="C11" s="131"/>
-      <c r="D11" s="107"/>
-      <c r="E11" s="107"/>
-      <c r="F11" s="107"/>
-      <c r="G11" s="107"/>
-      <c r="H11" s="107"/>
-      <c r="I11" s="134"/>
+      <c r="A11" s="111"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="115"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="118"/>
       <c r="J11" s="22" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="146.25" customHeight="1">
-      <c r="A12" s="177" t="s">
+      <c r="A12" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="178"/>
+      <c r="B12" s="123"/>
       <c r="C12" s="40" t="s">
         <v>27</v>
       </c>
@@ -7210,10 +7210,10 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="173.25" customHeight="1">
-      <c r="A13" s="177" t="s">
+      <c r="A13" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="178"/>
+      <c r="B13" s="123"/>
       <c r="C13" s="40" t="s">
         <v>29</v>
       </c>
@@ -7230,10 +7230,10 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="240">
-      <c r="A14" s="177" t="s">
+      <c r="A14" s="122" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="178"/>
+      <c r="B14" s="123"/>
       <c r="C14" s="40" t="s">
         <v>104</v>
       </c>
@@ -7250,10 +7250,10 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="322.5" customHeight="1">
-      <c r="A15" s="170" t="s">
+      <c r="A15" s="102" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="171"/>
+      <c r="B15" s="103"/>
       <c r="C15" s="59" t="s">
         <v>120</v>
       </c>
@@ -7270,18 +7270,18 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="76.5" customHeight="1">
-      <c r="A16" s="157" t="s">
+      <c r="A16" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="158"/>
-      <c r="C16" s="115" t="s">
+      <c r="B16" s="108"/>
+      <c r="C16" s="113" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="102"/>
+      <c r="D16" s="129"/>
       <c r="E16" s="38"/>
       <c r="F16" s="38"/>
-      <c r="G16" s="102"/>
-      <c r="H16" s="123"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="167"/>
       <c r="I16" s="42" t="s">
         <v>33</v>
       </c>
@@ -7290,14 +7290,14 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="58.5" customHeight="1">
-      <c r="A17" s="159"/>
-      <c r="B17" s="160"/>
-      <c r="C17" s="131"/>
-      <c r="D17" s="103"/>
+      <c r="A17" s="111"/>
+      <c r="B17" s="112"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="131"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="124"/>
+      <c r="G17" s="131"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="42" t="s">
         <v>34</v>
       </c>
@@ -7306,27 +7306,27 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="35.25" customHeight="1">
-      <c r="A18" s="157" t="s">
+      <c r="A18" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="158"/>
-      <c r="C18" s="115" t="s">
+      <c r="B18" s="108"/>
+      <c r="C18" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="165" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="165" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="165" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="165" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="128"/>
-      <c r="I18" s="155" t="s">
+      <c r="D18" s="134" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="134" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="134" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="134" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="172"/>
+      <c r="I18" s="124" t="s">
         <v>105</v>
       </c>
       <c r="J18" s="32" t="s">
@@ -7334,24 +7334,24 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A19" s="159"/>
-      <c r="B19" s="160"/>
-      <c r="C19" s="131"/>
-      <c r="D19" s="165"/>
-      <c r="E19" s="165"/>
-      <c r="F19" s="165"/>
-      <c r="G19" s="165"/>
-      <c r="H19" s="128"/>
-      <c r="I19" s="156"/>
+      <c r="A19" s="111"/>
+      <c r="B19" s="112"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="134"/>
+      <c r="E19" s="134"/>
+      <c r="F19" s="134"/>
+      <c r="G19" s="134"/>
+      <c r="H19" s="172"/>
+      <c r="I19" s="125"/>
       <c r="J19" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="108" customHeight="1">
-      <c r="A20" s="166" t="s">
+      <c r="A20" s="135" t="s">
         <v>171</v>
       </c>
-      <c r="B20" s="167"/>
+      <c r="B20" s="136"/>
       <c r="C20" s="71" t="s">
         <v>172</v>
       </c>
@@ -7378,10 +7378,10 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A21" s="161" t="s">
+      <c r="A21" s="126" t="s">
         <v>93</v>
       </c>
-      <c r="B21" s="161"/>
+      <c r="B21" s="126"/>
       <c r="C21" s="47" t="s">
         <v>94</v>
       </c>
@@ -7406,57 +7406,57 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="39" customHeight="1">
-      <c r="A22" s="162" t="s">
+      <c r="A22" s="127" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="162"/>
-      <c r="C22" s="143" t="s">
+      <c r="B22" s="127"/>
+      <c r="C22" s="128" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="112"/>
-      <c r="F22" s="168"/>
+      <c r="D22" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="163"/>
+      <c r="F22" s="137"/>
       <c r="G22" s="79"/>
       <c r="H22" s="79"/>
-      <c r="I22" s="163"/>
+      <c r="I22" s="132"/>
       <c r="J22" s="12" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="33.75" customHeight="1">
-      <c r="A23" s="162"/>
-      <c r="B23" s="162"/>
-      <c r="C23" s="143"/>
-      <c r="D23" s="108"/>
-      <c r="E23" s="113"/>
-      <c r="F23" s="169"/>
+      <c r="A23" s="127"/>
+      <c r="B23" s="127"/>
+      <c r="C23" s="128"/>
+      <c r="D23" s="130"/>
+      <c r="E23" s="164"/>
+      <c r="F23" s="138"/>
       <c r="G23" s="79"/>
       <c r="H23" s="79"/>
-      <c r="I23" s="163"/>
+      <c r="I23" s="132"/>
       <c r="J23" s="49" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="41.25" customHeight="1">
-      <c r="A24" s="162"/>
-      <c r="B24" s="162"/>
-      <c r="C24" s="143"/>
-      <c r="D24" s="103"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="169"/>
+      <c r="A24" s="127"/>
+      <c r="B24" s="127"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="131"/>
+      <c r="E24" s="165"/>
+      <c r="F24" s="138"/>
       <c r="G24" s="79"/>
       <c r="H24" s="79"/>
-      <c r="I24" s="163"/>
+      <c r="I24" s="132"/>
       <c r="J24" s="12" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="105.75" customHeight="1">
-      <c r="A25" s="162"/>
-      <c r="B25" s="162"/>
-      <c r="C25" s="164" t="s">
+      <c r="A25" s="127"/>
+      <c r="B25" s="127"/>
+      <c r="C25" s="133" t="s">
         <v>97</v>
       </c>
       <c r="D25" s="18" t="s">
@@ -7466,7 +7466,7 @@
       <c r="F25" s="79"/>
       <c r="G25" s="79"/>
       <c r="H25" s="79"/>
-      <c r="I25" s="125" t="s">
+      <c r="I25" s="169" t="s">
         <v>98</v>
       </c>
       <c r="J25" s="13" t="s">
@@ -7474,9 +7474,9 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="122.25" customHeight="1">
-      <c r="A26" s="162"/>
-      <c r="B26" s="162"/>
-      <c r="C26" s="164"/>
+      <c r="A26" s="127"/>
+      <c r="B26" s="127"/>
+      <c r="C26" s="133"/>
       <c r="D26" s="18" t="s">
         <v>3</v>
       </c>
@@ -7484,7 +7484,7 @@
       <c r="F26" s="79"/>
       <c r="G26" s="79"/>
       <c r="H26" s="79"/>
-      <c r="I26" s="125"/>
+      <c r="I26" s="169"/>
       <c r="J26" s="12" t="s">
         <v>175</v>
       </c>
@@ -7497,15 +7497,15 @@
       <c r="C27" s="153" t="s">
         <v>101</v>
       </c>
-      <c r="D27" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="112"/>
-      <c r="F27" s="118"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="126"/>
-      <c r="J27" s="126" t="s">
+      <c r="D27" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="163"/>
+      <c r="F27" s="178"/>
+      <c r="G27" s="170"/>
+      <c r="H27" s="170"/>
+      <c r="I27" s="139"/>
+      <c r="J27" s="139" t="s">
         <v>145</v>
       </c>
     </row>
@@ -7513,13 +7513,13 @@
       <c r="A28" s="151"/>
       <c r="B28" s="152"/>
       <c r="C28" s="154"/>
-      <c r="D28" s="103"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="118"/>
-      <c r="G28" s="111"/>
-      <c r="H28" s="111"/>
-      <c r="I28" s="127"/>
-      <c r="J28" s="127"/>
+      <c r="D28" s="131"/>
+      <c r="E28" s="165"/>
+      <c r="F28" s="178"/>
+      <c r="G28" s="171"/>
+      <c r="H28" s="171"/>
+      <c r="I28" s="140"/>
+      <c r="J28" s="140"/>
     </row>
     <row r="29" spans="1:10" ht="34.5" customHeight="1">
       <c r="A29" s="146" t="s">
@@ -7544,17 +7544,17 @@
       <c r="B30" s="150" t="s">
         <v>107</v>
       </c>
-      <c r="C30" s="115" t="s">
+      <c r="C30" s="113" t="s">
         <v>179</v>
       </c>
-      <c r="D30" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="E30" s="112"/>
-      <c r="F30" s="112"/>
-      <c r="G30" s="112"/>
-      <c r="H30" s="112"/>
-      <c r="I30" s="126" t="s">
+      <c r="D30" s="129" t="s">
+        <v>0</v>
+      </c>
+      <c r="E30" s="163"/>
+      <c r="F30" s="163"/>
+      <c r="G30" s="163"/>
+      <c r="H30" s="163"/>
+      <c r="I30" s="139" t="s">
         <v>109</v>
       </c>
       <c r="J30" s="52" t="s">
@@ -7564,13 +7564,13 @@
     <row r="31" spans="1:10" ht="14.25" customHeight="1">
       <c r="A31" s="148"/>
       <c r="B31" s="148"/>
-      <c r="C31" s="116"/>
-      <c r="D31" s="108"/>
-      <c r="E31" s="113"/>
-      <c r="F31" s="113"/>
-      <c r="G31" s="113"/>
-      <c r="H31" s="113"/>
-      <c r="I31" s="130"/>
+      <c r="C31" s="114"/>
+      <c r="D31" s="130"/>
+      <c r="E31" s="164"/>
+      <c r="F31" s="164"/>
+      <c r="G31" s="164"/>
+      <c r="H31" s="164"/>
+      <c r="I31" s="175"/>
       <c r="J31" s="17" t="s">
         <v>111</v>
       </c>
@@ -7578,13 +7578,13 @@
     <row r="32" spans="1:10" ht="32">
       <c r="A32" s="148"/>
       <c r="B32" s="149"/>
-      <c r="C32" s="116"/>
-      <c r="D32" s="129"/>
-      <c r="E32" s="114"/>
-      <c r="F32" s="114"/>
-      <c r="G32" s="114"/>
-      <c r="H32" s="114"/>
-      <c r="I32" s="127"/>
+      <c r="C32" s="114"/>
+      <c r="D32" s="173"/>
+      <c r="E32" s="174"/>
+      <c r="F32" s="174"/>
+      <c r="G32" s="174"/>
+      <c r="H32" s="174"/>
+      <c r="I32" s="140"/>
       <c r="J32" s="17" t="s">
         <v>112</v>
       </c>
@@ -7634,10 +7634,10 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="54.75" customHeight="1">
-      <c r="A35" s="121" t="s">
+      <c r="A35" s="141" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="122"/>
+      <c r="B35" s="142"/>
       <c r="C35" s="24"/>
       <c r="D35" s="18" t="s">
         <v>0</v>
@@ -7662,28 +7662,28 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="124.5" customHeight="1">
-      <c r="A36" s="120" t="s">
+      <c r="A36" s="143" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="120" t="s">
+      <c r="B36" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="143" t="s">
+      <c r="C36" s="128" t="s">
         <v>6</v>
       </c>
       <c r="D36" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E36" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="F36" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="G36" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="H36" s="102" t="s">
+      <c r="E36" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="G36" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="H36" s="129" t="s">
         <v>56</v>
       </c>
       <c r="I36" s="144" t="s">
@@ -7694,19 +7694,19 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="141" customHeight="1">
-      <c r="A37" s="120"/>
-      <c r="B37" s="120"/>
-      <c r="C37" s="143"/>
+      <c r="A37" s="143"/>
+      <c r="B37" s="143"/>
+      <c r="C37" s="128"/>
       <c r="D37" s="18"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="108"/>
-      <c r="G37" s="108"/>
-      <c r="H37" s="108"/>
+      <c r="E37" s="130"/>
+      <c r="F37" s="130"/>
+      <c r="G37" s="130"/>
+      <c r="H37" s="130"/>
       <c r="I37" s="144"/>
       <c r="J37" s="145"/>
     </row>
     <row r="38" spans="1:10" ht="208.5" customHeight="1">
-      <c r="A38" s="120"/>
+      <c r="A38" s="143"/>
       <c r="B38" s="89" t="s">
         <v>7</v>
       </c>
@@ -7714,17 +7714,17 @@
       <c r="D38" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="E38" s="103"/>
-      <c r="F38" s="103"/>
-      <c r="G38" s="103"/>
-      <c r="H38" s="103"/>
+      <c r="E38" s="131"/>
+      <c r="F38" s="131"/>
+      <c r="G38" s="131"/>
+      <c r="H38" s="131"/>
       <c r="I38" s="144"/>
       <c r="J38" s="25" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="39" customHeight="1">
-      <c r="A39" s="120"/>
+      <c r="A39" s="143"/>
       <c r="B39" s="89" t="s">
         <v>147</v>
       </c>
@@ -7750,7 +7750,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="50.25" customHeight="1">
-      <c r="A40" s="120"/>
+      <c r="A40" s="143"/>
       <c r="B40" s="89" t="s">
         <v>8</v>
       </c>
@@ -7776,7 +7776,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="161.25" customHeight="1">
-      <c r="A41" s="135" t="s">
+      <c r="A41" s="155" t="s">
         <v>193</v>
       </c>
       <c r="B41" s="89" t="s">
@@ -7806,15 +7806,15 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="163.5" customHeight="1">
-      <c r="A42" s="136"/>
+      <c r="A42" s="156"/>
       <c r="B42" s="65" t="s">
         <v>57</v>
       </c>
       <c r="C42" s="26"/>
-      <c r="D42" s="115" t="s">
-        <v>0</v>
-      </c>
-      <c r="E42" s="115" t="s">
+      <c r="D42" s="113" t="s">
+        <v>0</v>
+      </c>
+      <c r="E42" s="113" t="s">
         <v>0</v>
       </c>
       <c r="F42" s="18" t="s">
@@ -7834,11 +7834,11 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="314.25" customHeight="1">
-      <c r="A43" s="136"/>
+      <c r="A43" s="156"/>
       <c r="B43" s="91"/>
       <c r="C43" s="26"/>
-      <c r="D43" s="116"/>
-      <c r="E43" s="116"/>
+      <c r="D43" s="114"/>
+      <c r="E43" s="114"/>
       <c r="F43" s="18"/>
       <c r="G43" s="18"/>
       <c r="H43" s="18"/>
@@ -7848,11 +7848,11 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="117.75" customHeight="1">
-      <c r="A44" s="136"/>
+      <c r="A44" s="156"/>
       <c r="B44" s="91"/>
       <c r="C44" s="26"/>
-      <c r="D44" s="116"/>
-      <c r="E44" s="116"/>
+      <c r="D44" s="114"/>
+      <c r="E44" s="114"/>
       <c r="F44" s="18"/>
       <c r="G44" s="18"/>
       <c r="H44" s="18"/>
@@ -7862,13 +7862,13 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="230.25" customHeight="1">
-      <c r="A45" s="136"/>
+      <c r="A45" s="156"/>
       <c r="B45" s="91" t="s">
         <v>90</v>
       </c>
       <c r="C45" s="26"/>
-      <c r="D45" s="116"/>
-      <c r="E45" s="116"/>
+      <c r="D45" s="114"/>
+      <c r="E45" s="114"/>
       <c r="F45" s="38"/>
       <c r="G45" s="38"/>
       <c r="H45" s="38"/>
@@ -7878,177 +7878,177 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16">
-      <c r="A46" s="136"/>
+      <c r="A46" s="156"/>
       <c r="B46" s="89" t="s">
         <v>58</v>
       </c>
       <c r="C46" s="14"/>
-      <c r="D46" s="115" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" s="115" t="s">
-        <v>3</v>
-      </c>
-      <c r="F46" s="115" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="115" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="115" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="115"/>
+      <c r="D46" s="113" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="113" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="113" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="113" t="s">
+        <v>3</v>
+      </c>
+      <c r="H46" s="113" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="113"/>
       <c r="J46" s="9" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16">
-      <c r="A47" s="136"/>
+      <c r="A47" s="156"/>
       <c r="B47" s="89" t="s">
         <v>59</v>
       </c>
       <c r="C47" s="14"/>
-      <c r="D47" s="116"/>
-      <c r="E47" s="116"/>
-      <c r="F47" s="116"/>
-      <c r="G47" s="116"/>
-      <c r="H47" s="116"/>
-      <c r="I47" s="116"/>
+      <c r="D47" s="114"/>
+      <c r="E47" s="114"/>
+      <c r="F47" s="114"/>
+      <c r="G47" s="114"/>
+      <c r="H47" s="114"/>
+      <c r="I47" s="114"/>
       <c r="J47" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16">
-      <c r="A48" s="136"/>
+      <c r="A48" s="156"/>
       <c r="B48" s="89" t="s">
         <v>60</v>
       </c>
       <c r="C48" s="14"/>
-      <c r="D48" s="116"/>
-      <c r="E48" s="116"/>
-      <c r="F48" s="116"/>
-      <c r="G48" s="116"/>
-      <c r="H48" s="116"/>
-      <c r="I48" s="116"/>
+      <c r="D48" s="114"/>
+      <c r="E48" s="114"/>
+      <c r="F48" s="114"/>
+      <c r="G48" s="114"/>
+      <c r="H48" s="114"/>
+      <c r="I48" s="114"/>
       <c r="J48" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="16">
-      <c r="A49" s="136"/>
+      <c r="A49" s="156"/>
       <c r="B49" s="89" t="s">
         <v>61</v>
       </c>
       <c r="C49" s="14"/>
-      <c r="D49" s="116"/>
-      <c r="E49" s="116"/>
-      <c r="F49" s="116"/>
-      <c r="G49" s="116"/>
-      <c r="H49" s="116"/>
-      <c r="I49" s="116"/>
+      <c r="D49" s="114"/>
+      <c r="E49" s="114"/>
+      <c r="F49" s="114"/>
+      <c r="G49" s="114"/>
+      <c r="H49" s="114"/>
+      <c r="I49" s="114"/>
       <c r="J49" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="16">
-      <c r="A50" s="136"/>
+      <c r="A50" s="156"/>
       <c r="B50" s="89" t="s">
         <v>62</v>
       </c>
       <c r="C50" s="14"/>
-      <c r="D50" s="116"/>
-      <c r="E50" s="116"/>
-      <c r="F50" s="116"/>
-      <c r="G50" s="116"/>
-      <c r="H50" s="116"/>
-      <c r="I50" s="116"/>
+      <c r="D50" s="114"/>
+      <c r="E50" s="114"/>
+      <c r="F50" s="114"/>
+      <c r="G50" s="114"/>
+      <c r="H50" s="114"/>
+      <c r="I50" s="114"/>
       <c r="J50" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="16">
-      <c r="A51" s="136"/>
+      <c r="A51" s="156"/>
       <c r="B51" s="89" t="s">
         <v>63</v>
       </c>
       <c r="C51" s="14"/>
-      <c r="D51" s="116"/>
-      <c r="E51" s="116"/>
-      <c r="F51" s="116"/>
-      <c r="G51" s="116"/>
-      <c r="H51" s="116"/>
-      <c r="I51" s="116"/>
+      <c r="D51" s="114"/>
+      <c r="E51" s="114"/>
+      <c r="F51" s="114"/>
+      <c r="G51" s="114"/>
+      <c r="H51" s="114"/>
+      <c r="I51" s="114"/>
       <c r="J51" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="16">
-      <c r="A52" s="136"/>
+      <c r="A52" s="156"/>
       <c r="B52" s="89" t="s">
         <v>64</v>
       </c>
       <c r="C52" s="14"/>
-      <c r="D52" s="116"/>
-      <c r="E52" s="116"/>
-      <c r="F52" s="116"/>
-      <c r="G52" s="116"/>
-      <c r="H52" s="116"/>
-      <c r="I52" s="116"/>
+      <c r="D52" s="114"/>
+      <c r="E52" s="114"/>
+      <c r="F52" s="114"/>
+      <c r="G52" s="114"/>
+      <c r="H52" s="114"/>
+      <c r="I52" s="114"/>
       <c r="J52" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16">
-      <c r="A53" s="136"/>
+      <c r="A53" s="156"/>
       <c r="B53" s="89" t="s">
         <v>5</v>
       </c>
       <c r="C53" s="14"/>
-      <c r="D53" s="116"/>
-      <c r="E53" s="116"/>
-      <c r="F53" s="116"/>
-      <c r="G53" s="116"/>
-      <c r="H53" s="116"/>
-      <c r="I53" s="116"/>
+      <c r="D53" s="114"/>
+      <c r="E53" s="114"/>
+      <c r="F53" s="114"/>
+      <c r="G53" s="114"/>
+      <c r="H53" s="114"/>
+      <c r="I53" s="114"/>
       <c r="J53" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16">
-      <c r="A54" s="136"/>
+      <c r="A54" s="156"/>
       <c r="B54" s="89" t="s">
         <v>72</v>
       </c>
       <c r="C54" s="14"/>
-      <c r="D54" s="116"/>
-      <c r="E54" s="116"/>
-      <c r="F54" s="116"/>
-      <c r="G54" s="116"/>
-      <c r="H54" s="116"/>
-      <c r="I54" s="116"/>
+      <c r="D54" s="114"/>
+      <c r="E54" s="114"/>
+      <c r="F54" s="114"/>
+      <c r="G54" s="114"/>
+      <c r="H54" s="114"/>
+      <c r="I54" s="114"/>
       <c r="J54" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="18" customHeight="1">
-      <c r="A55" s="136"/>
+      <c r="A55" s="156"/>
       <c r="B55" s="89" t="s">
         <v>70</v>
       </c>
       <c r="C55" s="14"/>
-      <c r="D55" s="131"/>
-      <c r="E55" s="131"/>
-      <c r="F55" s="131"/>
-      <c r="G55" s="131"/>
-      <c r="H55" s="131"/>
-      <c r="I55" s="116"/>
+      <c r="D55" s="115"/>
+      <c r="E55" s="115"/>
+      <c r="F55" s="115"/>
+      <c r="G55" s="115"/>
+      <c r="H55" s="115"/>
+      <c r="I55" s="114"/>
       <c r="J55" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="32">
-      <c r="A56" s="136"/>
+      <c r="A56" s="156"/>
       <c r="B56" s="89" t="s">
         <v>78</v>
       </c>
@@ -8068,13 +8068,13 @@
       <c r="H56" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="I56" s="116"/>
+      <c r="I56" s="114"/>
       <c r="J56" s="35" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="32">
-      <c r="A57" s="136"/>
+      <c r="A57" s="156"/>
       <c r="B57" s="89" t="s">
         <v>79</v>
       </c>
@@ -8094,13 +8094,13 @@
       <c r="H57" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="I57" s="131"/>
+      <c r="I57" s="115"/>
       <c r="J57" s="35" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="32">
-      <c r="A58" s="136"/>
+      <c r="A58" s="156"/>
       <c r="B58" s="89" t="s">
         <v>127</v>
       </c>
@@ -8128,7 +8128,7 @@
       </c>
     </row>
     <row r="59" spans="1:10" ht="32">
-      <c r="A59" s="136"/>
+      <c r="A59" s="156"/>
       <c r="B59" s="89" t="s">
         <v>65</v>
       </c>
@@ -8154,7 +8154,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="32">
-      <c r="A60" s="136"/>
+      <c r="A60" s="156"/>
       <c r="B60" s="89" t="s">
         <v>71</v>
       </c>
@@ -8180,7 +8180,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="32">
-      <c r="A61" s="136"/>
+      <c r="A61" s="156"/>
       <c r="B61" s="89" t="s">
         <v>46</v>
       </c>
@@ -8206,7 +8206,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="32">
-      <c r="A62" s="136"/>
+      <c r="A62" s="156"/>
       <c r="B62" s="89" t="s">
         <v>66</v>
       </c>
@@ -8260,27 +8260,27 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16">
-      <c r="A64" s="137" t="s">
+      <c r="A64" s="157" t="s">
         <v>21</v>
       </c>
-      <c r="B64" s="138"/>
-      <c r="C64" s="143"/>
-      <c r="D64" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="E64" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="F64" s="102" t="s">
-        <v>3</v>
-      </c>
-      <c r="G64" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="H64" s="109" t="s">
-        <v>3</v>
-      </c>
-      <c r="I64" s="132" t="s">
+      <c r="B64" s="158"/>
+      <c r="C64" s="128"/>
+      <c r="D64" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="E64" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="G64" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="H64" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="I64" s="116" t="s">
         <v>146</v>
       </c>
       <c r="J64" s="30" t="s">
@@ -8288,94 +8288,94 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16">
-      <c r="A65" s="139"/>
-      <c r="B65" s="140"/>
-      <c r="C65" s="143"/>
-      <c r="D65" s="108"/>
-      <c r="E65" s="108"/>
-      <c r="F65" s="108"/>
-      <c r="G65" s="109"/>
-      <c r="H65" s="109"/>
-      <c r="I65" s="133"/>
+      <c r="A65" s="159"/>
+      <c r="B65" s="160"/>
+      <c r="C65" s="128"/>
+      <c r="D65" s="130"/>
+      <c r="E65" s="130"/>
+      <c r="F65" s="130"/>
+      <c r="G65" s="177"/>
+      <c r="H65" s="177"/>
+      <c r="I65" s="117"/>
       <c r="J65" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="16">
-      <c r="A66" s="139"/>
-      <c r="B66" s="140"/>
-      <c r="C66" s="143"/>
-      <c r="D66" s="108"/>
-      <c r="E66" s="108"/>
-      <c r="F66" s="108"/>
-      <c r="G66" s="109"/>
-      <c r="H66" s="109"/>
-      <c r="I66" s="133"/>
+      <c r="A66" s="159"/>
+      <c r="B66" s="160"/>
+      <c r="C66" s="128"/>
+      <c r="D66" s="130"/>
+      <c r="E66" s="130"/>
+      <c r="F66" s="130"/>
+      <c r="G66" s="177"/>
+      <c r="H66" s="177"/>
+      <c r="I66" s="117"/>
       <c r="J66" s="30" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="16">
-      <c r="A67" s="139"/>
-      <c r="B67" s="140"/>
-      <c r="C67" s="143"/>
-      <c r="D67" s="108"/>
-      <c r="E67" s="108"/>
-      <c r="F67" s="108"/>
-      <c r="G67" s="109"/>
-      <c r="H67" s="109"/>
-      <c r="I67" s="133"/>
+      <c r="A67" s="159"/>
+      <c r="B67" s="160"/>
+      <c r="C67" s="128"/>
+      <c r="D67" s="130"/>
+      <c r="E67" s="130"/>
+      <c r="F67" s="130"/>
+      <c r="G67" s="177"/>
+      <c r="H67" s="177"/>
+      <c r="I67" s="117"/>
       <c r="J67" s="15" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A68" s="139"/>
-      <c r="B68" s="140"/>
-      <c r="C68" s="143"/>
-      <c r="D68" s="108"/>
-      <c r="E68" s="108"/>
-      <c r="F68" s="108"/>
-      <c r="G68" s="109"/>
-      <c r="H68" s="109"/>
-      <c r="I68" s="133"/>
+      <c r="A68" s="159"/>
+      <c r="B68" s="160"/>
+      <c r="C68" s="128"/>
+      <c r="D68" s="130"/>
+      <c r="E68" s="130"/>
+      <c r="F68" s="130"/>
+      <c r="G68" s="177"/>
+      <c r="H68" s="177"/>
+      <c r="I68" s="117"/>
       <c r="J68" s="30" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16">
-      <c r="A69" s="139"/>
-      <c r="B69" s="140"/>
-      <c r="C69" s="143"/>
-      <c r="D69" s="108"/>
-      <c r="E69" s="108"/>
-      <c r="F69" s="108"/>
-      <c r="G69" s="109"/>
-      <c r="H69" s="109"/>
-      <c r="I69" s="133"/>
+      <c r="A69" s="159"/>
+      <c r="B69" s="160"/>
+      <c r="C69" s="128"/>
+      <c r="D69" s="130"/>
+      <c r="E69" s="130"/>
+      <c r="F69" s="130"/>
+      <c r="G69" s="177"/>
+      <c r="H69" s="177"/>
+      <c r="I69" s="117"/>
       <c r="J69" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A70" s="141"/>
-      <c r="B70" s="142"/>
-      <c r="C70" s="143"/>
-      <c r="D70" s="103"/>
-      <c r="E70" s="103"/>
-      <c r="F70" s="103"/>
-      <c r="G70" s="109"/>
-      <c r="H70" s="109"/>
-      <c r="I70" s="134"/>
+      <c r="A70" s="161"/>
+      <c r="B70" s="162"/>
+      <c r="C70" s="128"/>
+      <c r="D70" s="131"/>
+      <c r="E70" s="131"/>
+      <c r="F70" s="131"/>
+      <c r="G70" s="177"/>
+      <c r="H70" s="177"/>
+      <c r="I70" s="118"/>
       <c r="J70" s="30" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="64">
-      <c r="A71" s="121" t="s">
+      <c r="A71" s="141" t="s">
         <v>121</v>
       </c>
-      <c r="B71" s="122"/>
+      <c r="B71" s="142"/>
       <c r="C71" s="19"/>
       <c r="D71" s="18" t="s">
         <v>3</v>
@@ -8400,10 +8400,10 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="64">
-      <c r="A72" s="120" t="s">
+      <c r="A72" s="143" t="s">
         <v>38</v>
       </c>
-      <c r="B72" s="120"/>
+      <c r="B72" s="143"/>
       <c r="C72" s="61" t="s">
         <v>39</v>
       </c>
@@ -8671,6 +8671,82 @@
     </row>
   </sheetData>
   <mergeCells count="92">
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="E64:E70"/>
+    <mergeCell ref="F64:F70"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="G64:G70"/>
+    <mergeCell ref="H64:H70"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="H30:H32"/>
+    <mergeCell ref="I30:I32"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="I46:I57"/>
+    <mergeCell ref="I64:I70"/>
+    <mergeCell ref="A41:A62"/>
+    <mergeCell ref="D46:D55"/>
+    <mergeCell ref="E46:E55"/>
+    <mergeCell ref="F46:F55"/>
+    <mergeCell ref="G46:G55"/>
+    <mergeCell ref="H46:H55"/>
+    <mergeCell ref="A64:B70"/>
+    <mergeCell ref="C64:C70"/>
+    <mergeCell ref="D64:D70"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:A40"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="H36:H38"/>
+    <mergeCell ref="I36:I40"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B26"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="F22:F24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="A5:B6"/>
@@ -8687,82 +8763,6 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:G5"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B26"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:A40"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="H36:H38"/>
-    <mergeCell ref="I36:I40"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="I46:I57"/>
-    <mergeCell ref="I64:I70"/>
-    <mergeCell ref="A41:A62"/>
-    <mergeCell ref="D46:D55"/>
-    <mergeCell ref="E46:E55"/>
-    <mergeCell ref="F46:F55"/>
-    <mergeCell ref="G46:G55"/>
-    <mergeCell ref="H46:H55"/>
-    <mergeCell ref="A64:B70"/>
-    <mergeCell ref="C64:C70"/>
-    <mergeCell ref="D64:D70"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="H30:H32"/>
-    <mergeCell ref="I30:I32"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="F7:F11"/>
-    <mergeCell ref="E64:E70"/>
-    <mergeCell ref="F64:F70"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="F36:F38"/>
-    <mergeCell ref="G64:G70"/>
-    <mergeCell ref="H64:H70"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F27:F28"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
